--- a/data/trans_orig/IP37-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>32212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28975</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41014</t>
+          <t>40533</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54404</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69952</t>
+          <t>69553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27695</t>
+          <t>27673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29257</t>
+          <t>29656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44805</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60500</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77061</t>
+          <t>77679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64849</t>
+          <t>65049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79943</t>
+          <t>80470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130477</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>151667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26934</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59191</t>
+          <t>60214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81404</t>
+          <t>82320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32675</t>
+          <t>33013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46029</t>
+          <t>46203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>33768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44788</t>
+          <t>44606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70142</t>
+          <t>69303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87607</t>
+          <t>87671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>39065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41680</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59145</t>
+          <t>59984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40629</t>
+          <t>40881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>55337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45997</t>
+          <t>46285</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61838</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91132</t>
+          <t>90881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112566</t>
+          <t>111667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>27539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33341</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49182</t>
+          <t>48894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65488</t>
+          <t>66387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86922</t>
+          <t>87173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>171440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197088</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>188033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214065</t>
+          <t>215929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>365387</t>
+          <t>366403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>404206</t>
+          <t>403945</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>102979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131032</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102878</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>128910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214225</t>
+          <t>214486</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253044</t>
+          <t>252028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61209</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>72939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60174</t>
+          <t>58091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71608</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124139</t>
+          <t>125660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141136</t>
+          <t>142287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94656</t>
+          <t>95475</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111107</t>
+          <t>110720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95590</t>
+          <t>96423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113335</t>
+          <t>114044</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196786</t>
+          <t>197132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220863</t>
+          <t>220910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53763</t>
+          <t>53716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77840</t>
+          <t>77494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59561</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72360</t>
+          <t>72247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62776</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>111552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131639</t>
+          <t>130954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>32201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>32918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54063</t>
+          <t>53139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67906</t>
+          <t>67824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68626</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83664</t>
+          <t>83368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126987</t>
+          <t>126164</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149219</t>
+          <t>146739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,16%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>37532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38576</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48654</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70886</t>
+          <t>71709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284784</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312239</t>
+          <t>312540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290227</t>
+          <t>287798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317646</t>
+          <t>318138</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580782</t>
+          <t>582699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>623064</t>
+          <t>623538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>76557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97047</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124466</t>
+          <t>126895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180726</t>
+          <t>180252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223008</t>
+          <t>221091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48695</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60159</t>
+          <t>59980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>49409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90314</t>
+          <t>90848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106837</t>
+          <t>107046</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25627</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70526</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84679</t>
+          <t>84119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88036</t>
+          <t>87655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103160</t>
+          <t>103340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162581</t>
+          <t>164012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183741</t>
+          <t>183403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37577</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>44269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65091</t>
+          <t>63660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70689</t>
+          <t>70782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83753</t>
+          <t>83612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>61863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77505</t>
+          <t>76353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138571</t>
+          <t>138193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157879</t>
+          <t>156915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18256</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>33898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33589</t>
+          <t>34553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52897</t>
+          <t>53275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58253</t>
+          <t>57905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73268</t>
+          <t>73063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64460</t>
+          <t>63705</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113589</t>
+          <t>112517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133583</t>
+          <t>132745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>19552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43985</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>65051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>262856</t>
+          <t>263178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>288726</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255559</t>
+          <t>254604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283291</t>
+          <t>282717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525049</t>
+          <t>526669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>563719</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73603</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83551</t>
+          <t>84125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165452</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204122</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>44230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55177</t>
+          <t>54981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>80078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94696</t>
+          <t>94508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32273</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35336</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50673</t>
+          <t>50248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34388</t>
+          <t>34160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74745</t>
+          <t>75034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95091</t>
+          <t>94886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15325</t>
+          <t>15750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30662</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55553</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70918</t>
+          <t>71670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104731</t>
+          <t>105768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63404</t>
+          <t>64871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84424</t>
+          <t>84392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142777</t>
+          <t>143656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185074</t>
+          <t>185370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52842</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49089</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>50883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93476</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>162495</t>
+          <t>163670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204839</t>
+          <t>205255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162932</t>
+          <t>164795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192773</t>
+          <t>193078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338564</t>
+          <t>339051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390416</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>63346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>91629</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123652</t>
+          <t>125858</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175504</t>
+          <t>175017</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP37-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34951</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29022</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40861</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27218</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22074</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32212</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>21892</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31542</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34951</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>28997</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>40533</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,68%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54327</t>
+          <t>53549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69553</t>
+          <t>69366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21719</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15809</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27648</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15321</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10327</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10997</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20647</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21719</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16137</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27673</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,32%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56670</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56670</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56670</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>42539</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>42539</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>42539</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>56670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72765</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64647</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79847</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,92%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>74,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>69559</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>61973</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>77679</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>61502</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>76508</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>66,89%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>59,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>72765</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>65049</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>80470</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>67,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129561</t>
+          <t>131270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151667</t>
+          <t>153825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,6%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35121</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28039</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43239</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,08%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>34436</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26316</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42022</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27487</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42493</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>33,11%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35121</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27416</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>42837</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60214</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82320</t>
+          <t>80611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107886</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107886</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107886</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103995</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103995</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103995</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>107886</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>107886</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>107886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39331</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33527</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44472</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>68,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39754</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33013</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46203</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32706</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>46471</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39331</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33768</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>44606</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>68,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69303</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87671</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17878</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12737</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23682</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>32324</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25875</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39065</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25607</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>39372</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,85%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17878</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12603</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23441</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>41339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59984</t>
+          <t>58938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57209</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57209</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57209</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>72078</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>72078</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>72078</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>57209</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>57209</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>57209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>53952</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46266</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61147</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>47770</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40881</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55337</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40440</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55109</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>57,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>53952</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>46285</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>60990</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>56,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90881</t>
+          <t>90124</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111667</t>
+          <t>110642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>41227</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34032</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48913</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35106</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27539</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41995</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>27767</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42436</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>42,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41227</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34189</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>48894</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66387</t>
+          <t>67412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87173</t>
+          <t>87930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>95179</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>95179</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>95179</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>82876</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>82876</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>82876</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>95179</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>95179</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>95179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>186230</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>213697</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>58,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>171440</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>198509</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>171439</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199853</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>56,86%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>188033</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>215929</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>59,33%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>366403</t>
+          <t>364768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>403945</t>
+          <t>404199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>115944</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>103246</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130713</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>117187</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102979</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>130048</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101635</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>130049</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,87%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>43,14%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>115944</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101014</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>128910</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>40,67%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214486</t>
+          <t>214232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252028</t>
+          <t>253663</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>316943</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>316943</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66253</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59661</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71702</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>72,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>67590</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60662</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>72939</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>61299</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>73471</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>79,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>66253</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>58091</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>71238</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>124324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142287</t>
+          <t>141441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16543</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23135</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17034</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11685</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23962</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11153</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23325</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>28,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16543</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11558</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24705</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>25979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>43096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>84624</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>84624</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>84624</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105394</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>95320</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>113921</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>66,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>104160</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>95475</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>110720</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>95806</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>111689</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,79%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>105394</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>96423</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>114044</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197132</t>
+          <t>197292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>220910</t>
+          <t>221157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38690</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30163</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48764</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>26382</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19822</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35067</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18853</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>34736</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>38690</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>30040</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>47661</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>53469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77494</t>
+          <t>77334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>144084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>144084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>144084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>130542</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>130542</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>130542</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>144084</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>144084</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>144084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56021</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48646</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62075</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>69,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66440</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60206</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>72247</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>59913</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>72397</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>79,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56021</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48411</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>69,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111552</t>
+          <t>112952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130954</t>
+          <t>130866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,86%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24591</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18537</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31966</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16820</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11013</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23054</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10863</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23347</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24591</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18278</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32201</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>50920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>83260</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>83260</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>83260</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>80612</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>80612</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>80612</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>76554</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68990</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83848</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61366</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53139</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>67824</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>53114</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>68205</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>74,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>76554</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>67213</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>83368</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,41%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126164</t>
+          <t>126774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146739</t>
+          <t>147350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30648</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23354</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38212</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29305</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22847</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37532</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22466</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37557</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30648</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23834</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39989</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,59%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51134</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71709</t>
+          <t>71099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>107202</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>107202</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>107202</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>90671</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>90671</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>90671</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>107202</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>107202</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>107202</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>289252</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>319160</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>434</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>284619</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>312540</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>285815</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>312603</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>287798</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>318138</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>582699</t>
+          <t>583210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>623538</t>
+          <t>621768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>110471</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>95533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>125441</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>89541</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>76557</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>104478</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>76494</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>103282</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>110471</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>96555</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>126895</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>180252</t>
+          <t>182022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>221091</t>
+          <t>220580</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>414693</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>414693</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>414693</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>559</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>389097</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>389097</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>389097</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>414693</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>414693</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>414693</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44657</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38765</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49567</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>54722</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48303</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59980</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>47986</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>60186</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>76,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>44657</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38949</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>49409</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90848</t>
+          <t>91521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107046</t>
+          <t>107072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15858</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10948</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21750</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17227</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11969</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23646</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11763</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>23963</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15858</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11106</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21566</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>26,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>25392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60515</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60515</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60515</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>71949</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>71949</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>71949</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60515</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60515</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>95965</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>87745</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>102513</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>78182</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>71548</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>84119</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>71522</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>84245</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>76,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>95965</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>87655</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>103340</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>76,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164012</t>
+          <t>163109</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183403</t>
+          <t>184302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29648</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23100</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37868</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>23876</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17939</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30510</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17813</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30536</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>29648</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22273</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37958</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>43370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63660</t>
+          <t>64563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>125613</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>125613</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>125613</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>102058</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>102058</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>102058</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>125613</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>125613</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>125613</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70264</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>62237</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77179</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>77857</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>70782</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83612</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>70690</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>83133</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>81,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>73,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70264</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61863</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76353</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>137852</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156915</t>
+          <t>157598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25497</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18582</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33524</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17850</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12095</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24925</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12574</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25017</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>18,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25497</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19408</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33898</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>33870</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53275</t>
+          <t>53616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>95761</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>95761</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>95761</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>95707</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>95707</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>95707</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>95761</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>95761</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>95761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57590</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>49785</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64105</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>66053</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>57905</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73063</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>58698</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73071</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>71,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,52%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>57590</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>49097</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>63705</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>67,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112517</t>
+          <t>113553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132745</t>
+          <t>134883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -5764,67 +5764,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>27363</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20848</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35168</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>26562</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19552</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34710</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19544</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>33917</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>28,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27363</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21248</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35856</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>42685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>64015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>84953</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>84953</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>84953</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92615</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92615</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92615</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>84953</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>84953</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>84953</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,74 +5989,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>254378</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>281816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>420</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>263178</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>289108</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>262174</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>289089</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>79,79%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>254604</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>282717</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>69,4%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>77,07%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>802</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>526669</t>
+          <t>525292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>564503</t>
+          <t>563262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>98366</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>85026</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>112464</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>85515</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73221</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>99151</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>73240</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>100155</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>20,21%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>98366</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>84125</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112238</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164668</t>
+          <t>165909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>203879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366842</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362329</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362329</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362329</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10274</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7547</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12476</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13475</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10284</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15986</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>58,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6716</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7248</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23,14%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17532</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17532</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17532</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>29549</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>29549</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>29549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42981</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37442</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>46827</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71,02%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37370</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31716</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41964</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>74,21%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,99%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>83,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50550</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44230</t>
+          <t>28858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>87920</t>
+          <t>77022</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80078</t>
+          <t>69394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94508</t>
+          <t>82954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5894</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15279</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28,98%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12984</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8390</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18638</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>24571</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52721</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52721</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52721</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40703</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33821</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47014</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>43197</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35705</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50248</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>33140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>46659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>85496</t>
+          <t>80435</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75034</t>
+          <t>70438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94886</t>
+          <t>89084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20959</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14648</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27841</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22801</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15750</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30293</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>44787</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35412</t>
+          <t>36138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55264</t>
+          <t>54784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61662</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61662</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>61662</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>65998</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>65998</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>65998</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>130298</t>
+          <t>125222</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>130298</t>
+          <t>125222</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>130298</t>
+          <t>125222</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68498</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58501</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>77185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>86414</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>71670</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>105768</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>74266</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>50234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84392</t>
+          <t>67645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>160681</t>
+          <t>127603</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143656</t>
+          <t>114792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185370</t>
+          <t>139615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37928</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29241</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>47925</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>37346</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17992</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>52090</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>39413</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>30873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>77341</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50883</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>90152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>123760</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>123760</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>123760</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>98518</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>98518</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>98518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>236253</t>
+          <t>204944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>236253</t>
+          <t>204944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>236253</t>
+          <t>204944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>150383</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>175572</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>63,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>163670</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>205255</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>131478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193078</t>
+          <t>155723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>339051</t>
+          <t>289848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388210</t>
+          <t>326240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72616</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>59500</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>84689</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>77187</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93974</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>78410</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>67374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91629</t>
+          <t>91619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>153647</t>
+          <t>151026</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125858</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175017</t>
+          <t>168321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>235072</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>257644</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256424</t>
+          <t>223097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>514068</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
